--- a/admin/SMART_CART_DATA.xlsx
+++ b/admin/SMART_CART_DATA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nikhi\AppData\Local\Packages\5319275A.51895FA4EA97F_cv1g1gvanyjgm\LocalState\sessions\49F8129B3C16783374DD6F4184E9D65DF6DD9718\transfers\2026-09\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nikhi\Projects\SmartCart\admin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7CF8DD5-BBF8-4BF3-930A-5E5DA166DB00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{752EE3E4-2391-4AAB-8B1A-20BBA311B656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="28800" windowHeight="15480" xr2:uid="{96E75DC7-6899-49CE-BE8E-4385CDA2FB43}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{96E75DC7-6899-49CE-BE8E-4385CDA2FB43}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="498">
   <si>
     <t>product_id</t>
   </si>
@@ -87,9 +87,6 @@
     <t>reviews</t>
   </si>
   <si>
-    <t>ai_context_text</t>
-  </si>
-  <si>
     <t>LAP001</t>
   </si>
   <si>
@@ -126,9 +123,6 @@
     <t>[{"rating":5,"comment":"Great gaming performance"},{"rating":3,"comment":"Battery life is average"}]</t>
   </si>
   <si>
-    <t>AeroBook Pro 15 by AeroTech is a gaming laptop priced at 74999 INR. It features Intel i7 12th Gen processor, 16GB RAM, RTX 3050 GPU and 512GB SSD. Rated 4.3 from 120 reviews. Users praise performance but mention moderate battery life.</t>
-  </si>
-  <si>
     <t>CLO001</t>
   </si>
   <si>
@@ -162,9 +156,6 @@
     <t>[{"rating":4,"comment":"Comfortable fabric"},{"rating":2,"comment":"Size runs slightly small"}]</t>
   </si>
   <si>
-    <t>Slim Fit Cotton T-Shirt by UrbanWear is priced at 999 INR. Made from cotton with slim fit design and solid pattern. Rated 4.1 from 58 reviews. Customers like comfort but mention sizing concerns.</t>
-  </si>
-  <si>
     <t>PHN001</t>
   </si>
   <si>
@@ -195,9 +186,6 @@
     <t>[{"rating":5,"comment":"Camera quality is excellent"},{"rating":4,"comment":"Battery lasts full day"}]</t>
   </si>
   <si>
-    <t>Nova X5 Pro by NovaTech is priced at 28999 INR. It comes with Snapdragon 8 Gen 1 processor, 8GB RAM, 108MP camera and 5000mAh battery. Rated 4.4 from 210 reviews. Users appreciate camera and display performance.</t>
-  </si>
-  <si>
     <t>Img_URL</t>
   </si>
   <si>
@@ -231,9 +219,6 @@
     <t>[{"rating":4,"comment":"Great value for money"},{"rating":4,"comment":"Battery lasts 2 days"}]</t>
   </si>
   <si>
-    <t>MaxPhone 12 Ultra by TechMax is an affordable smartphone at 14999 INR. Features MediaTek Helio G88, 6GB RAM, 50MP camera and massive 6000mAh battery. Rated 4.0 from 145 reviews. Customers praise battery life and value.</t>
-  </si>
-  <si>
     <t>TAB001</t>
   </si>
   <si>
@@ -261,9 +246,6 @@
     <t>[{"rating":5,"comment":"Perfect for note-taking"},{"rating":4,"comment":"Great for watching movies"}]</t>
   </si>
   <si>
-    <t>AeroPad Ultra 11 by AeroTech is a premium tablet priced at 45999 INR. Features Snapdragon 870, 8GB RAM, 11-inch 2K display and stylus support. Rated 4.5 from 89 reviews. Users love it for productivity and media consumption.</t>
-  </si>
-  <si>
     <t>HEAD001</t>
   </si>
   <si>
@@ -294,9 +276,6 @@
     <t>[{"rating":5,"comment":"Noise cancellation is amazing"},{"rating":4,"comment":"Very comfortable for long use"}]</t>
   </si>
   <si>
-    <t>WavePro Noise Cancelling by SoundWave is priced at 8999 INR. Features Bluetooth 5.2, active noise cancellation and 30-hour battery. Rated 4.6 from 234 reviews. Praised for excellent ANC and comfort.</t>
-  </si>
-  <si>
     <t>HEAD002</t>
   </si>
   <si>
@@ -324,9 +303,6 @@
     <t>[{"rating":4,"comment":"Good sound quality"},{"rating":4,"comment":"Comfortable fit"}]</t>
   </si>
   <si>
-    <t>BudsPro TWS Earbuds by SoundWave priced at 2999 INR. Offers Bluetooth 5.0, 24-hour battery with case and IPX4 water resistance. Rated 4.2 from 312 reviews. Users appreciate sound quality and fit.</t>
-  </si>
-  <si>
     <t>CAM001</t>
   </si>
   <si>
@@ -357,9 +333,6 @@
     <t>[{"rating":5,"comment":"Outstanding image quality"},{"rating":4,"comment":"Great for beginners"}]</t>
   </si>
   <si>
-    <t>ProShot DSLR 5000 by PixelPro is priced at 52999 INR. Features 24MP APS-C sensor, 4K video and optical viewfinder. Rated 4.7 from 67 reviews. Highly regarded for image quality.</t>
-  </si>
-  <si>
     <t>WATCH001</t>
   </si>
   <si>
@@ -390,9 +363,6 @@
     <t>[{"rating":4,"comment":"Accurate fitness tracking"},{"rating":5,"comment":"Battery life is excellent"}]</t>
   </si>
   <si>
-    <t>FitWatch Pro 3 by FitTech priced at 12999 INR. Features 1.4-inch AMOLED display, 7-day battery, heart rate and SpO2 sensors. Rated 4.3 from 178 reviews. Users love fitness tracking accuracy.</t>
-  </si>
-  <si>
     <t>LAP002</t>
   </si>
   <si>
@@ -417,9 +387,6 @@
     <t>[{"rating":4,"comment":"Very portable"},{"rating":4,"comment":"Good for office work"}]</t>
   </si>
   <si>
-    <t>MaxBook Air 14 by TechMax priced at 42999 INR. Features Intel i5 11th Gen, 8GB RAM, 512GB SSD and weighs only 1.3kg. Rated 4.1 from 95 reviews. Appreciated for portability.</t>
-  </si>
-  <si>
     <t>TV001</t>
   </si>
   <si>
@@ -450,9 +417,6 @@
     <t>[{"rating":5,"comment":"Picture quality is superb"},{"rating":4,"comment":"Great for movies"}]</t>
   </si>
   <si>
-    <t>UltraView 55 4K Smart TV by VisionTech priced at 38999 INR. Features 4K UHD resolution, HDR10, Android TV and Dolby Audio. Rated 4.4 from 156 reviews. Praised for picture quality.</t>
-  </si>
-  <si>
     <t>SPEAK001</t>
   </si>
   <si>
@@ -480,9 +444,6 @@
     <t>[{"rating":4,"comment":"Amazing bass"},{"rating":5,"comment":"Very loud and clear"}]</t>
   </si>
   <si>
-    <t>BoomBox Bluetooth Speaker by SoundWave priced at 3999 INR. Features Bluetooth 5.0, 12-hour battery, IPX7 waterproof and 20W output. Rated 4.3 from 203 reviews. Users love bass quality.</t>
-  </si>
-  <si>
     <t>MON001</t>
   </si>
   <si>
@@ -513,9 +474,6 @@
     <t>[{"rating":5,"comment":"Perfect for photo editing"},{"rating":4,"comment":"Great color accuracy"}]</t>
   </si>
   <si>
-    <t>ProDisplay 27 QHD by ViewMax priced at 24999 INR. Features 2560x1440 resolution, 75Hz refresh rate, IPS panel and 99% sRGB coverage. Rated 4.5 from 82 reviews. Excellent for creative work.</t>
-  </si>
-  <si>
     <t>KEYB001</t>
   </si>
   <si>
@@ -546,9 +504,6 @@
     <t>[{"rating":5,"comment":"Typing feels amazing"},{"rating":4,"comment":"RGB looks great"}]</t>
   </si>
   <si>
-    <t>MechPro RGB Keyboard by TypeMaster priced at 4999 INR. Features Cherry MX switches, RGB backlighting and wired USB connection. Rated 4.4 from 127 reviews. Great tactile feedback.</t>
-  </si>
-  <si>
     <t>MOUSE001</t>
   </si>
   <si>
@@ -576,9 +531,6 @@
     <t>[{"rating":4,"comment":"Very responsive"},{"rating":4,"comment":"Comfortable grip"}]</t>
   </si>
   <si>
-    <t>GameX Pro Gaming Mouse by TypeMaster priced at 2499 INR. Features 16000 DPI, 8 programmable buttons, 70-hour battery and RGB lighting. Rated 4.2 from 164 reviews. Praised for precision.</t>
-  </si>
-  <si>
     <t>POW001</t>
   </si>
   <si>
@@ -606,9 +558,6 @@
     <t>[{"rating":4,"comment":"Charges my phone 4 times"},{"rating":4,"comment":"Compact and portable"}]</t>
   </si>
   <si>
-    <t>PowerMax 20000mAh by ChargePlus priced at 1999 INR. Features 20000mAh capacity, fast charging, multiple ports with 18W output. Rated 4.1 from 289 reviews. Great value for capacity.</t>
-  </si>
-  <si>
     <t>CLO002</t>
   </si>
   <si>
@@ -639,9 +588,6 @@
     <t>[{"rating":5,"comment":"Perfect fit and comfort"},{"rating":4,"comment":"Good quality denim"}]</t>
   </si>
   <si>
-    <t>Classic Blue Slim Fit Jeans by DenimCraft priced at 2499 INR. Features premium denim with stretch, stone washed finish. Rated 4.3 from 142 reviews. Customers praise fit and comfort.</t>
-  </si>
-  <si>
     <t>CLO003</t>
   </si>
   <si>
@@ -672,9 +618,6 @@
     <t>[{"rating":5,"comment":"Very warm and comfortable"},{"rating":4,"comment":"Great for cold weather"}]</t>
   </si>
   <si>
-    <t>Winter Puffer Jacket by OutdoorPro priced at 3999 INR. Features synthetic insulation, water resistance and detachable hood. Rated 4.5 from 98 reviews. Excellent warmth for winter.</t>
-  </si>
-  <si>
     <t>CLO004</t>
   </si>
   <si>
@@ -705,9 +648,6 @@
     <t>[{"rating":4,"comment":"Good quality fabric"},{"rating":4,"comment":"Perfect for office"}]</t>
   </si>
   <si>
-    <t>Formal White Dress Shirt by FormalFit priced at 1799 INR. Made from premium cotton with spread collar and regular fit. Rated 4.2 from 123 reviews. Great for formal wear.</t>
-  </si>
-  <si>
     <t>CLO005</t>
   </si>
   <si>
@@ -738,9 +678,6 @@
     <t>[{"rating":5,"comment":"Beautiful dress"},{"rating":4,"comment":"Comfortable and stylish"}]</t>
   </si>
   <si>
-    <t>Floral Maxi Dress by ChicStyle priced at 2999 INR. Made from rayon with vibrant floral print and A-line fit. Rated 4.4 from 87 reviews. Perfect for summer occasions.</t>
-  </si>
-  <si>
     <t>CLO006</t>
   </si>
   <si>
@@ -768,9 +705,6 @@
     <t>[{"rating":4,"comment":"Very comfortable"},{"rating":5,"comment":"Perfect for winter"}]</t>
   </si>
   <si>
-    <t>Cotton Pullover Hoodie by UrbanWear priced at 1799 INR. Features cotton blend material, kangaroo pocket and regular fit. Rated 4.3 from 156 reviews. Great for casual wear.</t>
-  </si>
-  <si>
     <t>CLO007</t>
   </si>
   <si>
@@ -798,9 +732,6 @@
     <t>[{"rating":4,"comment":"Good fit"},{"rating":4,"comment":"Comfortable for all day wear"}]</t>
   </si>
   <si>
-    <t>Formal Pleated Trousers by FormalFit priced at 1999 INR. Made from polyester blend with double pleats and regular fit. Rated 4.1 from 94 reviews. Ideal for office wear.</t>
-  </si>
-  <si>
     <t>CLO008</t>
   </si>
   <si>
@@ -831,9 +762,6 @@
     <t>[{"rating":4,"comment":"Very comfortable for running"},{"rating":4,"comment":"Dries quickly"}]</t>
   </si>
   <si>
-    <t>Athletic Running Shorts by ActiveSport priced at 899 INR. Features moisture-wicking polyester and quick-dry technology. Rated 4.2 from 178 reviews. Perfect for active lifestyle.</t>
-  </si>
-  <si>
     <t>CLO009</t>
   </si>
   <si>
@@ -864,9 +792,6 @@
     <t>[{"rating":5,"comment":"Very warm and soft"},{"rating":4,"comment":"Good quality"}]</t>
   </si>
   <si>
-    <t>Wool Blend Pullover Sweater by CozyKnit priced at 2499 INR. Made from soft wool blend with crew neck. Rated 4.4 from 112 reviews. Excellent warmth for winter.</t>
-  </si>
-  <si>
     <t>CLO010</t>
   </si>
   <si>
@@ -897,9 +822,6 @@
     <t>[{"rating":4,"comment":"Good quality fabric"},{"rating":4,"comment":"Versatile shirt"}]</t>
   </si>
   <si>
-    <t>Classic Pique Polo Shirt by SportFit priced at 1299 INR. Made from cotton pique with regular fit. Rated 4.2 from 134 reviews. Great for casual and semi-formal wear.</t>
-  </si>
-  <si>
     <t>CLO011</t>
   </si>
   <si>
@@ -927,9 +849,6 @@
     <t>[{"rating":5,"comment":"Perfect fit and quality"},{"rating":4,"comment":"Great for meetings"}]</t>
   </si>
   <si>
-    <t>Tailored Business Blazer by FormalFit priced at 4999 INR. Features slim fit, notch lapel and full lining. Rated 4.5 from 76 reviews. Excellent for professional settings.</t>
-  </si>
-  <si>
     <t>CLO012</t>
   </si>
   <si>
@@ -957,9 +876,6 @@
     <t>[{"rating":4,"comment":"Very comfortable"},{"rating":5,"comment":"Perfect for yoga"}]</t>
   </si>
   <si>
-    <t>High Waist Yoga Leggings by ActiveSport priced at 1199 INR. Features compression fit, high waist and side pocket. Rated 4.3 from 198 reviews. Ideal for yoga and fitness.</t>
-  </si>
-  <si>
     <t>CLO013</t>
   </si>
   <si>
@@ -984,9 +900,6 @@
     <t>[{"rating":4,"comment":"Great for gym"},{"rating":4,"comment":"Breathable fabric"}]</t>
   </si>
   <si>
-    <t>Breathable Training Tank by ActiveSport priced at 699 INR. Features moisture-wicking polyester with racerback design. Rated 4.1 from 167 reviews. Perfect for gym workouts.</t>
-  </si>
-  <si>
     <t>CLO014</t>
   </si>
   <si>
@@ -1014,9 +927,6 @@
     <t>[{"rating":4,"comment":"Very soft and comfortable"},{"rating":4,"comment":"Great for layering"}]</t>
   </si>
   <si>
-    <t>Button Front Knit Cardigan by CozyKnit priced at 2199 INR. Made from soft acrylic blend with button closure. Rated 4.3 from 105 reviews. Perfect layering piece.</t>
-  </si>
-  <si>
     <t>CLO015</t>
   </si>
   <si>
@@ -1041,9 +951,6 @@
     <t>[{"rating":4,"comment":"Comfortable for jogging"},{"rating":4,"comment":"Good quality"}]</t>
   </si>
   <si>
-    <t>Complete Training Tracksuit by ActiveSport priced at 3499 INR. Includes zip-up jacket and elastic waist pants. Rated 4.2 from 89 reviews. Great for training and casual wear.</t>
-  </si>
-  <si>
     <t>HOME001</t>
   </si>
   <si>
@@ -1077,9 +984,6 @@
     <t>[{"rating":5,"comment":"Excellent quality"},{"rating":4,"comment":"Easy to clean"}]</t>
   </si>
   <si>
-    <t>Non-Stick Cookware Set by ChefPro priced at 3999 INR. Includes 5 pieces with durable non-stick coating. Rated 4.4 from 156 reviews. Easy to clean and maintain.</t>
-  </si>
-  <si>
     <t>HOME002</t>
   </si>
   <si>
@@ -1110,9 +1014,6 @@
     <t>[{"rating":4,"comment":"Grinds very well"},{"rating":5,"comment":"Powerful motor"}]</t>
   </si>
   <si>
-    <t>PowerBlend Pro 750W Mixer by PowerBlend priced at 4499 INR. Features 750W motor, 3 stainless steel jars and 3 speed settings. Rated 4.3 from 189 reviews. Powerful grinding performance.</t>
-  </si>
-  <si>
     <t>HOME003</t>
   </si>
   <si>
@@ -1143,9 +1044,6 @@
     <t>[{"rating":4,"comment":"Great suction power"},{"rating":4,"comment":"Easy to use"}]</t>
   </si>
   <si>
-    <t>Bagless Vacuum Cleaner by CleanMaster priced at 6999 INR. Features 1400W power, 2L capacity, HEPA filter and 5 attachments. Rated 4.2 from 134 reviews. Excellent suction power.</t>
-  </si>
-  <si>
     <t>HOME004</t>
   </si>
   <si>
@@ -1176,9 +1074,6 @@
     <t>[{"rating":5,"comment":"Excellent for allergies"},{"rating":4,"comment":"Very quiet"}]</t>
   </si>
   <si>
-    <t>Smart Air Purifier by PureAir priced at 8999 INR. Features True HEPA filter, 300 sq ft coverage, app control and quiet operation. Rated 4.5 from 167 reviews. Great for allergies.</t>
-  </si>
-  <si>
     <t>HOME005</t>
   </si>
   <si>
@@ -1209,9 +1104,6 @@
     <t>[{"rating":5,"comment":"Water tastes great"},{"rating":4,"comment":"Easy installation"}]</t>
   </si>
   <si>
-    <t>RO Water Purifier by AquaPure priced at 12999 INR. Features 7-stage RO+UV+UF purification, 7L capacity. Rated 4.4 from 198 reviews. Ensures safe drinking water.</t>
-  </si>
-  <si>
     <t>HOME006</t>
   </si>
   <si>
@@ -1242,9 +1134,6 @@
     <t>[{"rating":4,"comment":"Makes great coffee"},{"rating":5,"comment":"Love the timer feature"}]</t>
   </si>
   <si>
-    <t>Automatic Coffee Machine by BrewMaster priced at 5499 INR. Features programmable timer, 10-cup capacity, 3 brew strengths. Rated 4.3 from 145 reviews. Perfect morning coffee.</t>
-  </si>
-  <si>
     <t>HOME007</t>
   </si>
   <si>
@@ -1275,9 +1164,6 @@
     <t>[{"rating":4,"comment":"Beautiful design"},{"rating":4,"comment":"Good quality"}]</t>
   </si>
   <si>
-    <t>Ceramic Dinner Set by DineWell priced at 3499 INR. Includes 24 pieces serving 6, microwave and dishwasher safe. Rated 4.2 from 112 reviews. Elegant for family dining.</t>
-  </si>
-  <si>
     <t>HOME008</t>
   </si>
   <si>
@@ -1305,9 +1191,6 @@
     <t>[{"rating":5,"comment":"Cooks very fast"},{"rating":4,"comment":"Very safe to use"}]</t>
   </si>
   <si>
-    <t>Stainless Steel Pressure Cooker by ChefPro priced at 2999 INR. Features 5L capacity, induction compatible, 3 safety valves. Rated 4.4 from 223 reviews. Fast and safe cooking.</t>
-  </si>
-  <si>
     <t>HOME009</t>
   </si>
   <si>
@@ -1338,9 +1221,6 @@
     <t>[{"rating":4,"comment":"Very versatile"},{"rating":5,"comment":"Baking works great"}]</t>
   </si>
   <si>
-    <t>Convection Microwave by CookFast priced at 11999 INR. Features 28L capacity, 900W power, multiple cooking functions and 101 auto-cook menus. Rated 4.3 from 176 reviews. Perfect for all cooking needs.</t>
-  </si>
-  <si>
     <t>HOME010</t>
   </si>
   <si>
@@ -1371,9 +1251,6 @@
     <t>[{"rating":4,"comment":"Very soft and comfortable"},{"rating":4,"comment":"Good quality cotton"}]</t>
   </si>
   <si>
-    <t>Cotton Bedsheet Set by SleepWell priced at 1999 INR. Made from 100% cotton, king size with 200 thread count. Rated 4.2 from 189 reviews. Soft and breathable for good sleep.</t>
-  </si>
-  <si>
     <t>BOOK001</t>
   </si>
   <si>
@@ -1407,9 +1284,6 @@
     <t>[{"rating":5,"comment":"Could not put it down"},{"rating":4,"comment":"Great plot twists"}]</t>
   </si>
   <si>
-    <t>The Midnight Garden by Sarah Mitchell priced at 399 INR. Mystery thriller with 384 pages published by ReadMore. Rated 4.4 from 234 reviews. Engaging plot with unexpected twists.</t>
-  </si>
-  <si>
     <t>BOOK002</t>
   </si>
   <si>
@@ -1440,9 +1314,6 @@
     <t>[{"rating":5,"comment":"Life-changing book"},{"rating":4,"comment":"Very practical advice"}]</t>
   </si>
   <si>
-    <t>Mindful Success by Dr. James Cooper priced at 449 INR. Self-help book with 256 pages on mindfulness and goal achievement. Rated 4.5 from 189 reviews. Practical and transformative.</t>
-  </si>
-  <si>
     <t>BOOK003</t>
   </si>
   <si>
@@ -1470,9 +1341,6 @@
     <t>[{"rating":5,"comment":"Best Python resource"},{"rating":5,"comment":"Very comprehensive"}]</t>
   </si>
   <si>
-    <t>Python for Data Science by Michael Chen priced at 699 INR. Technical book with 512 pages covering Python for data science. Rated 4.6 from 267 reviews. Comprehensive and well-structured.</t>
-  </si>
-  <si>
     <t>BOOK004</t>
   </si>
   <si>
@@ -1500,9 +1368,6 @@
     <t>[{"rating":4,"comment":"Very inspiring"},{"rating":5,"comment":"Motivational read"}]</t>
   </si>
   <si>
-    <t>Journey to Innovation by Robert Williams priced at 499 INR. Biography with 368 pages about tech entrepreneur journey. Rated 4.3 from 156 reviews. Inspiring and motivational.</t>
-  </si>
-  <si>
     <t>BOOK005</t>
   </si>
   <si>
@@ -1530,9 +1395,6 @@
     <t>[{"rating":5,"comment":"Authentic recipes"},{"rating":4,"comment":"Easy to follow"}]</t>
   </si>
   <si>
-    <t>Indian Cuisine Masterclass by Chef Priya Sharma priced at 599 INR. Cooking book with 320 pages of Indian recipes. Rated 4.5 from 178 reviews. Authentic and easy to follow.</t>
-  </si>
-  <si>
     <t>BOOK006</t>
   </si>
   <si>
@@ -1560,9 +1422,6 @@
     <t>[{"rating":5,"comment":"Mind-blowing content"},{"rating":5,"comment":"Beautifully explained"}]</t>
   </si>
   <si>
-    <t>Cosmos Explained by Dr. Neil Robertson priced at 549 INR. Science book with 432 pages about space and universe. Rated 4.6 from 198 reviews. Fascinating and educational.</t>
-  </si>
-  <si>
     <t>BOOK007</t>
   </si>
   <si>
@@ -1590,9 +1449,6 @@
     <t>[{"rating":5,"comment":"Kids love it"},{"rating":4,"comment":"Beautiful illustrations"}]</t>
   </si>
   <si>
-    <t>Adventures in Wonderland by Emma Thompson priced at 349 INR. Children book with 128 illustrated pages for ages 5-10. Rated 4.4 from 145 reviews. Magical and engaging.</t>
-  </si>
-  <si>
     <t>BOOK008</t>
   </si>
   <si>
@@ -1620,9 +1476,6 @@
     <t>[{"rating":4,"comment":"Very insightful"},{"rating":5,"comment":"Must-read for managers"}]</t>
   </si>
   <si>
-    <t>Leadership Principles by Margaret Foster priced at 599 INR. Business book with 296 pages on modern leadership. Rated 4.4 from 167 reviews. Essential for managers and leaders.</t>
-  </si>
-  <si>
     <t>BOOK009</t>
   </si>
   <si>
@@ -1650,9 +1503,6 @@
     <t>[{"rating":5,"comment":"Very informative"},{"rating":4,"comment":"Well researched"}]</t>
   </si>
   <si>
-    <t>Ancient Civilizations by Dr. Thomas Anderson priced at 649 INR. History book with 456 pages about ancient cultures. Rated 4.5 from 134 reviews. Comprehensive and well-researched.</t>
-  </si>
-  <si>
     <t>BOOK010</t>
   </si>
   <si>
@@ -1678,9 +1528,6 @@
   </si>
   <si>
     <t>[{"rating":4,"comment":"Very romantic"},{"rating":5,"comment":"Loved the characters"}]</t>
-  </si>
-  <si>
-    <t>Hearts Entwined by Jessica Martin priced at 379 INR. Romance novel with 312 pages set in modern times. Rated 4.2 from 212 reviews. Heartwarming and relatable.</t>
   </si>
 </sst>
 </file>
@@ -2071,21 +1918,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{847E05F2-1784-483A-B357-09DE8401BB00}">
   <dimension ref="A1:S51"/>
-  <sheetFormatPr defaultColWidth="14.33203125" defaultRowHeight="27" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="14.33203125" defaultRowHeight="59.25" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.33203125" style="3"/>
     <col min="2" max="4" width="14.33203125" style="1"/>
-    <col min="5" max="6" width="19.88671875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="32" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.77734375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.88671875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.88671875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="45.109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="71.44140625" style="1" customWidth="1"/>
     <col min="9" max="10" width="14.33203125" style="1"/>
-    <col min="11" max="11" width="28" style="1" customWidth="1"/>
-    <col min="12" max="18" width="14.33203125" style="1"/>
+    <col min="11" max="11" width="19.77734375" style="1" customWidth="1"/>
+    <col min="12" max="14" width="14.33203125" style="1"/>
+    <col min="15" max="15" width="56.44140625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="59.109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="45.44140625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="90.44140625" style="1" customWidth="1"/>
     <col min="19" max="19" width="25" style="1" customWidth="1"/>
     <col min="20" max="16384" width="14.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" s="3" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2102,7 +1954,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>5</v>
@@ -2140,40 +1992,38 @@
       <c r="R1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2" spans="1:19" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="I2" s="5">
         <v>74999</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K2" s="5">
         <v>10</v>
@@ -2188,51 +2038,48 @@
         <v>120</v>
       </c>
       <c r="O2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="Q2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="R2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="R2" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:19" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="F3" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>48</v>
       </c>
       <c r="I3" s="5">
         <v>28999</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K3" s="5">
         <v>8</v>
@@ -2247,51 +2094,48 @@
         <v>210</v>
       </c>
       <c r="O3" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="R3" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="P3" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="R3" s="6" t="s">
+    </row>
+    <row r="4" spans="1:19" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="B4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+      <c r="E4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>60</v>
       </c>
       <c r="I4" s="5">
         <v>14999</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K4" s="5">
         <v>12</v>
@@ -2306,51 +2150,48 @@
         <v>145</v>
       </c>
       <c r="O4" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="B5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="Q4" s="6" t="s">
+      <c r="D5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="R4" s="6" t="s">
+      <c r="F5" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="H5" s="6" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="I5" s="5">
         <v>45999</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K5" s="5">
         <v>5</v>
@@ -2365,51 +2206,48 @@
         <v>89</v>
       </c>
       <c r="O5" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q5" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="R5" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="P5" s="7" t="s">
+      <c r="D6" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="Q5" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="R5" s="6" t="s">
+      <c r="F6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="S5" s="1" t="s">
+      <c r="H6" s="6" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="I6" s="5">
         <v>8999</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K6" s="5">
         <v>20</v>
@@ -2424,51 +2262,48 @@
         <v>234</v>
       </c>
       <c r="O6" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="R6" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="F7" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="Q6" s="6" t="s">
+      <c r="H7" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="R6" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="I7" s="5">
         <v>2999</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K7" s="5">
         <v>15</v>
@@ -2483,51 +2318,48 @@
         <v>312</v>
       </c>
       <c r="O7" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="R7" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="P7" s="7" t="s">
+      <c r="F8" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="Q7" s="6" t="s">
+      <c r="H8" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="R7" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="I8" s="5">
         <v>52999</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K8" s="5">
         <v>8</v>
@@ -2542,51 +2374,48 @@
         <v>67</v>
       </c>
       <c r="O8" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q8" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="R8" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="P8" s="7" t="s">
+      <c r="H9" s="6" t="s">
         <v>104</v>
-      </c>
-      <c r="Q8" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="R8" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>113</v>
       </c>
       <c r="I9" s="5">
         <v>12999</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K9" s="5">
         <v>10</v>
@@ -2601,51 +2430,48 @@
         <v>178</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>20</v>
-      </c>
       <c r="D10" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="I10" s="5">
         <v>42999</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K10" s="5">
         <v>12</v>
@@ -2660,51 +2486,48 @@
         <v>95</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="Q10" s="6" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="I11" s="5">
         <v>38999</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K11" s="5">
         <v>15</v>
@@ -2719,51 +2542,48 @@
         <v>156</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="I12" s="5">
         <v>3999</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K12" s="5">
         <v>18</v>
@@ -2778,51 +2598,48 @@
         <v>203</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="Q12" s="6" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="S12" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="I13" s="5">
         <v>24999</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K13" s="5">
         <v>10</v>
@@ -2837,51 +2654,48 @@
         <v>82</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="I14" s="5">
         <v>4999</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K14" s="5">
         <v>20</v>
@@ -2896,51 +2710,48 @@
         <v>127</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="S14" s="1" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="I15" s="5">
         <v>2499</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K15" s="5">
         <v>15</v>
@@ -2955,51 +2766,48 @@
         <v>164</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="I16" s="5">
         <v>1999</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K16" s="5">
         <v>25</v>
@@ -3014,51 +2822,48 @@
         <v>289</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="P16" s="7" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="F17" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="H17" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>37</v>
       </c>
       <c r="I17" s="5">
         <v>999</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K17" s="5">
         <v>15</v>
@@ -3073,51 +2878,48 @@
         <v>58</v>
       </c>
       <c r="O17" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q17" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="P17" s="7" t="s">
+      <c r="R17" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="Q17" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="R17" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="S17" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="I18" s="5">
         <v>2499</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K18" s="5">
         <v>20</v>
@@ -3132,51 +2934,48 @@
         <v>142</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="Q18" s="6" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="S18" s="1" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I19" s="5">
         <v>3999</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K19" s="5">
         <v>18</v>
@@ -3191,51 +2990,48 @@
         <v>98</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="Q19" s="6" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="I20" s="5">
         <v>1799</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K20" s="5">
         <v>12</v>
@@ -3250,51 +3046,48 @@
         <v>123</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>219</v>
+        <v>200</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="Q20" s="6" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="I21" s="5">
         <v>2999</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K21" s="5">
         <v>22</v>
@@ -3309,51 +3102,48 @@
         <v>87</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="B22" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="D22" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>34</v>
-      </c>
       <c r="E22" s="5" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
       <c r="I22" s="5">
         <v>1799</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K22" s="5">
         <v>15</v>
@@ -3368,51 +3158,48 @@
         <v>156</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>240</v>
+        <v>219</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="Q22" s="6" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="S22" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="I23" s="5">
         <v>1999</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K23" s="5">
         <v>10</v>
@@ -3427,51 +3214,48 @@
         <v>94</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="Q23" s="6" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="S23" s="1" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>256</v>
+        <v>233</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
       <c r="I24" s="5">
         <v>899</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K24" s="5">
         <v>20</v>
@@ -3486,51 +3270,48 @@
         <v>178</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="P24" s="7" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="Q24" s="6" t="s">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="S24" s="1" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>267</v>
+        <v>243</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>268</v>
+        <v>244</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>271</v>
+        <v>247</v>
       </c>
       <c r="I25" s="5">
         <v>2499</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K25" s="5">
         <v>15</v>
@@ -3545,51 +3326,48 @@
         <v>112</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>273</v>
+        <v>249</v>
       </c>
       <c r="Q25" s="6" t="s">
-        <v>274</v>
+        <v>250</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="S25" s="1" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>277</v>
+        <v>252</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>278</v>
+        <v>253</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>279</v>
+        <v>254</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>281</v>
+        <v>256</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="I26" s="5">
         <v>1299</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K26" s="5">
         <v>18</v>
@@ -3604,51 +3382,48 @@
         <v>134</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>283</v>
+        <v>258</v>
       </c>
       <c r="P26" s="7" t="s">
-        <v>284</v>
+        <v>259</v>
       </c>
       <c r="Q26" s="6" t="s">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="S26" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>288</v>
+        <v>262</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>289</v>
+        <v>263</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>291</v>
+        <v>265</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="I27" s="5">
         <v>4999</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K27" s="5">
         <v>12</v>
@@ -3663,51 +3438,48 @@
         <v>76</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>293</v>
+        <v>267</v>
       </c>
       <c r="P27" s="7" t="s">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="S27" s="1" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
-        <v>298</v>
+        <v>271</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>299</v>
+        <v>272</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>300</v>
+        <v>273</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>301</v>
+        <v>274</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>302</v>
+        <v>275</v>
       </c>
       <c r="I28" s="5">
         <v>1199</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K28" s="5">
         <v>25</v>
@@ -3722,51 +3494,48 @@
         <v>198</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>303</v>
+        <v>276</v>
       </c>
       <c r="P28" s="7" t="s">
-        <v>304</v>
+        <v>277</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>305</v>
+        <v>278</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="S28" s="1" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
-        <v>308</v>
+        <v>280</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>309</v>
+        <v>281</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>310</v>
+        <v>282</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>311</v>
+        <v>283</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>312</v>
+        <v>284</v>
       </c>
       <c r="I29" s="5">
         <v>699</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K29" s="5">
         <v>20</v>
@@ -3781,51 +3550,48 @@
         <v>167</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="P29" s="7" t="s">
-        <v>313</v>
+        <v>285</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>314</v>
+        <v>286</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
-        <v>317</v>
+        <v>288</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>318</v>
+        <v>289</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>268</v>
+        <v>244</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>319</v>
+        <v>290</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>320</v>
+        <v>291</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>321</v>
+        <v>292</v>
       </c>
       <c r="I30" s="5">
         <v>2199</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K30" s="5">
         <v>15</v>
@@ -3840,51 +3606,48 @@
         <v>105</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>322</v>
+        <v>293</v>
       </c>
       <c r="P30" s="7" t="s">
-        <v>323</v>
+        <v>294</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>324</v>
+        <v>295</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>327</v>
+        <v>297</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>328</v>
+        <v>298</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>329</v>
+        <v>299</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>331</v>
+        <v>301</v>
       </c>
       <c r="I31" s="5">
         <v>3499</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K31" s="5">
         <v>20</v>
@@ -3899,51 +3662,48 @@
         <v>89</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="P31" s="7" t="s">
-        <v>332</v>
+        <v>302</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>333</v>
+        <v>303</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="S31" s="1" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
-        <v>336</v>
+        <v>305</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>337</v>
+        <v>306</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>338</v>
+        <v>307</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>339</v>
+        <v>308</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>340</v>
+        <v>309</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>341</v>
+        <v>310</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>342</v>
+        <v>311</v>
       </c>
       <c r="I32" s="5">
         <v>3999</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K32" s="5">
         <v>18</v>
@@ -3958,51 +3718,48 @@
         <v>156</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>343</v>
+        <v>312</v>
       </c>
       <c r="P32" s="7" t="s">
-        <v>344</v>
+        <v>313</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>345</v>
+        <v>314</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="S32" s="1" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
-        <v>348</v>
+        <v>316</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>337</v>
+        <v>306</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>349</v>
+        <v>317</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>350</v>
+        <v>318</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>353</v>
+        <v>321</v>
       </c>
       <c r="I33" s="5">
         <v>4499</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K33" s="5">
         <v>15</v>
@@ -4017,51 +3774,48 @@
         <v>189</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>354</v>
+        <v>322</v>
       </c>
       <c r="P33" s="7" t="s">
-        <v>355</v>
+        <v>323</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>356</v>
+        <v>324</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="S33" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
-        <v>359</v>
+        <v>326</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>337</v>
+        <v>306</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>360</v>
+        <v>327</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>361</v>
+        <v>328</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>362</v>
+        <v>329</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>363</v>
+        <v>330</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>364</v>
+        <v>331</v>
       </c>
       <c r="I34" s="5">
         <v>6999</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K34" s="5">
         <v>20</v>
@@ -4076,51 +3830,48 @@
         <v>134</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>365</v>
+        <v>332</v>
       </c>
       <c r="P34" s="7" t="s">
-        <v>366</v>
+        <v>333</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>367</v>
+        <v>334</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="S34" s="1" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
-        <v>370</v>
+        <v>336</v>
       </c>
       <c r="B35" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>371</v>
-      </c>
       <c r="D35" s="5" t="s">
-        <v>372</v>
+        <v>338</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>373</v>
+        <v>339</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>374</v>
+        <v>340</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>375</v>
+        <v>341</v>
       </c>
       <c r="I35" s="5">
         <v>8999</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K35" s="5">
         <v>15</v>
@@ -4135,51 +3886,48 @@
         <v>167</v>
       </c>
       <c r="O35" s="6" t="s">
-        <v>376</v>
+        <v>342</v>
       </c>
       <c r="P35" s="7" t="s">
-        <v>377</v>
+        <v>343</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>378</v>
+        <v>344</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>379</v>
-      </c>
-      <c r="S35" s="1" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
-        <v>381</v>
+        <v>346</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>337</v>
+        <v>306</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>382</v>
+        <v>347</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>383</v>
+        <v>348</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>384</v>
+        <v>349</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>385</v>
+        <v>350</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>386</v>
+        <v>351</v>
       </c>
       <c r="I36" s="5">
         <v>12999</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K36" s="5">
         <v>18</v>
@@ -4194,51 +3942,48 @@
         <v>198</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>387</v>
+        <v>352</v>
       </c>
       <c r="P36" s="7" t="s">
-        <v>388</v>
+        <v>353</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>389</v>
+        <v>354</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="S36" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
-        <v>392</v>
+        <v>356</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>337</v>
+        <v>306</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>393</v>
+        <v>357</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>394</v>
+        <v>358</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>395</v>
+        <v>359</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>396</v>
+        <v>360</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>397</v>
+        <v>361</v>
       </c>
       <c r="I37" s="5">
         <v>5499</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K37" s="5">
         <v>20</v>
@@ -4253,51 +3998,48 @@
         <v>145</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>398</v>
+        <v>362</v>
       </c>
       <c r="P37" s="7" t="s">
-        <v>399</v>
+        <v>363</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>400</v>
+        <v>364</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>401</v>
-      </c>
-      <c r="S37" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>403</v>
+        <v>366</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>337</v>
+        <v>306</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>404</v>
+        <v>367</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>405</v>
+        <v>368</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>406</v>
+        <v>369</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>407</v>
+        <v>370</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>408</v>
+        <v>371</v>
       </c>
       <c r="I38" s="5">
         <v>3499</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K38" s="5">
         <v>22</v>
@@ -4312,51 +4054,48 @@
         <v>112</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>409</v>
+        <v>372</v>
       </c>
       <c r="P38" s="7" t="s">
-        <v>410</v>
+        <v>373</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>411</v>
+        <v>374</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>412</v>
-      </c>
-      <c r="S38" s="1" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>414</v>
+        <v>376</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>337</v>
+        <v>306</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>415</v>
+        <v>377</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>339</v>
+        <v>308</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>416</v>
+        <v>378</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>417</v>
+        <v>379</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>418</v>
+        <v>380</v>
       </c>
       <c r="I39" s="5">
         <v>2999</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K39" s="5">
         <v>15</v>
@@ -4371,51 +4110,48 @@
         <v>223</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>419</v>
+        <v>381</v>
       </c>
       <c r="P39" s="7" t="s">
-        <v>420</v>
+        <v>382</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>421</v>
+        <v>383</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>422</v>
-      </c>
-      <c r="S39" s="1" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>424</v>
+        <v>385</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>337</v>
+        <v>306</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>425</v>
+        <v>386</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>426</v>
+        <v>387</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>427</v>
+        <v>388</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>428</v>
+        <v>389</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>429</v>
+        <v>390</v>
       </c>
       <c r="I40" s="5">
         <v>11999</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K40" s="5">
         <v>18</v>
@@ -4430,51 +4166,48 @@
         <v>176</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>430</v>
+        <v>391</v>
       </c>
       <c r="P40" s="7" t="s">
-        <v>431</v>
+        <v>392</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>432</v>
+        <v>393</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>433</v>
-      </c>
-      <c r="S40" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>435</v>
+        <v>395</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>337</v>
+        <v>306</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>436</v>
+        <v>396</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>437</v>
+        <v>397</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>438</v>
+        <v>398</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>439</v>
+        <v>399</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="I41" s="5">
         <v>1999</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K41" s="5">
         <v>25</v>
@@ -4489,51 +4222,48 @@
         <v>189</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>441</v>
+        <v>401</v>
       </c>
       <c r="P41" s="7" t="s">
-        <v>442</v>
+        <v>402</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>443</v>
+        <v>403</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="S41" s="1" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>446</v>
+        <v>405</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>447</v>
+        <v>406</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>448</v>
+        <v>407</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>449</v>
+        <v>408</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>450</v>
+        <v>409</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>451</v>
+        <v>410</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>452</v>
+        <v>411</v>
       </c>
       <c r="I42" s="5">
         <v>399</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K42" s="5">
         <v>20</v>
@@ -4548,51 +4278,48 @@
         <v>234</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>453</v>
+        <v>412</v>
       </c>
       <c r="P42" s="7" t="s">
-        <v>454</v>
+        <v>413</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>455</v>
+        <v>414</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>456</v>
-      </c>
-      <c r="S42" s="1" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>458</v>
+        <v>416</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>447</v>
+        <v>406</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>459</v>
+        <v>417</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>460</v>
+        <v>418</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>461</v>
+        <v>419</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>462</v>
+        <v>420</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>463</v>
+        <v>421</v>
       </c>
       <c r="I43" s="5">
         <v>449</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K43" s="5">
         <v>15</v>
@@ -4607,51 +4334,48 @@
         <v>189</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>464</v>
+        <v>422</v>
       </c>
       <c r="P43" s="7" t="s">
-        <v>465</v>
+        <v>423</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>466</v>
+        <v>424</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>467</v>
-      </c>
-      <c r="S43" s="1" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>469</v>
+        <v>426</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>447</v>
+        <v>406</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>470</v>
+        <v>427</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>471</v>
+        <v>428</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>472</v>
+        <v>429</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>473</v>
+        <v>430</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>474</v>
+        <v>431</v>
       </c>
       <c r="I44" s="5">
         <v>699</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K44" s="5">
         <v>18</v>
@@ -4666,51 +4390,48 @@
         <v>267</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>464</v>
+        <v>422</v>
       </c>
       <c r="P44" s="7" t="s">
-        <v>475</v>
+        <v>432</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>476</v>
+        <v>433</v>
       </c>
       <c r="R44" s="6" t="s">
-        <v>477</v>
-      </c>
-      <c r="S44" s="1" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>479</v>
+        <v>435</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>447</v>
+        <v>406</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>481</v>
+        <v>437</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>482</v>
+        <v>438</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>483</v>
+        <v>439</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>484</v>
+        <v>440</v>
       </c>
       <c r="I45" s="5">
         <v>499</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K45" s="5">
         <v>20</v>
@@ -4725,51 +4446,48 @@
         <v>156</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>453</v>
+        <v>412</v>
       </c>
       <c r="P45" s="7" t="s">
-        <v>485</v>
+        <v>441</v>
       </c>
       <c r="Q45" s="6" t="s">
-        <v>486</v>
+        <v>442</v>
       </c>
       <c r="R45" s="6" t="s">
-        <v>487</v>
-      </c>
-      <c r="S45" s="1" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>489</v>
+        <v>444</v>
       </c>
       <c r="B46" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="E46" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="C46" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>491</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>492</v>
-      </c>
       <c r="F46" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>493</v>
+        <v>448</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>494</v>
+        <v>449</v>
       </c>
       <c r="I46" s="5">
         <v>599</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K46" s="5">
         <v>15</v>
@@ -4784,51 +4502,48 @@
         <v>178</v>
       </c>
       <c r="O46" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="P46" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="Q46" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="R46" s="6" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="P46" s="7" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q46" s="6" t="s">
-        <v>496</v>
-      </c>
-      <c r="R46" s="6" t="s">
-        <v>497</v>
-      </c>
-      <c r="S46" s="1" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="4" t="s">
-        <v>499</v>
-      </c>
       <c r="B47" s="5" t="s">
-        <v>447</v>
+        <v>406</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>500</v>
+        <v>454</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>501</v>
+        <v>455</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>502</v>
+        <v>456</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>503</v>
+        <v>457</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>504</v>
+        <v>458</v>
       </c>
       <c r="I47" s="5">
         <v>549</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K47" s="5">
         <v>12</v>
@@ -4843,51 +4558,48 @@
         <v>198</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>453</v>
+        <v>412</v>
       </c>
       <c r="P47" s="7" t="s">
-        <v>505</v>
+        <v>459</v>
       </c>
       <c r="Q47" s="6" t="s">
-        <v>506</v>
+        <v>460</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>507</v>
-      </c>
-      <c r="S47" s="1" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
-        <v>509</v>
+        <v>462</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>447</v>
+        <v>406</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>510</v>
+        <v>463</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>511</v>
+        <v>464</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>512</v>
+        <v>465</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>513</v>
+        <v>466</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>514</v>
+        <v>467</v>
       </c>
       <c r="I48" s="5">
         <v>349</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K48" s="5">
         <v>20</v>
@@ -4902,51 +4614,48 @@
         <v>145</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>453</v>
+        <v>412</v>
       </c>
       <c r="P48" s="7" t="s">
-        <v>515</v>
+        <v>468</v>
       </c>
       <c r="Q48" s="6" t="s">
-        <v>516</v>
+        <v>469</v>
       </c>
       <c r="R48" s="6" t="s">
-        <v>517</v>
-      </c>
-      <c r="S48" s="1" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>519</v>
+        <v>471</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>447</v>
+        <v>406</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>520</v>
+        <v>472</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>521</v>
+        <v>473</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>522</v>
+        <v>474</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>523</v>
+        <v>475</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>524</v>
+        <v>476</v>
       </c>
       <c r="I49" s="5">
         <v>599</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K49" s="5">
         <v>18</v>
@@ -4961,51 +4670,48 @@
         <v>167</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>453</v>
+        <v>412</v>
       </c>
       <c r="P49" s="7" t="s">
-        <v>525</v>
+        <v>477</v>
       </c>
       <c r="Q49" s="6" t="s">
-        <v>526</v>
+        <v>478</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>527</v>
-      </c>
-      <c r="S49" s="1" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>529</v>
+        <v>480</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>447</v>
+        <v>406</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>530</v>
+        <v>481</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>531</v>
+        <v>482</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>532</v>
+        <v>483</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>533</v>
+        <v>484</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>534</v>
+        <v>485</v>
       </c>
       <c r="I50" s="5">
         <v>649</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K50" s="5">
         <v>15</v>
@@ -5020,51 +4726,48 @@
         <v>134</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>453</v>
+        <v>412</v>
       </c>
       <c r="P50" s="7" t="s">
-        <v>535</v>
+        <v>486</v>
       </c>
       <c r="Q50" s="6" t="s">
-        <v>536</v>
+        <v>487</v>
       </c>
       <c r="R50" s="6" t="s">
-        <v>537</v>
-      </c>
-      <c r="S50" s="1" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>539</v>
+        <v>489</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>447</v>
+        <v>406</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>540</v>
+        <v>490</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>541</v>
+        <v>491</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>542</v>
+        <v>492</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>543</v>
+        <v>493</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>544</v>
+        <v>494</v>
       </c>
       <c r="I51" s="5">
         <v>379</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K51" s="5">
         <v>22</v>
@@ -5079,19 +4782,16 @@
         <v>212</v>
       </c>
       <c r="O51" s="6" t="s">
-        <v>464</v>
+        <v>422</v>
       </c>
       <c r="P51" s="7" t="s">
-        <v>545</v>
+        <v>495</v>
       </c>
       <c r="Q51" s="6" t="s">
-        <v>546</v>
+        <v>496</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>547</v>
-      </c>
-      <c r="S51" s="1" t="s">
-        <v>548</v>
+        <v>497</v>
       </c>
     </row>
   </sheetData>
